--- a/estimation/notsensor/DenseModel/Dense_1st_torch_optimized/IWALQQ_1st_correction/angle/4_fold/135.xlsx
+++ b/estimation/notsensor/DenseModel/Dense_1st_torch_optimized/IWALQQ_1st_correction/angle/4_fold/135.xlsx
@@ -426,13 +426,13 @@
         <v>-15.9696054908409</v>
       </c>
       <c r="E2">
-        <v>-11.09222292158167</v>
+        <v>-9.261175212846235</v>
       </c>
       <c r="F2">
-        <v>-3.130417958142298</v>
+        <v>-3.338472371764228</v>
       </c>
       <c r="G2">
-        <v>-6.643425841615002</v>
+        <v>-4.907653074225629</v>
       </c>
     </row>
     <row r="3" spans="1:7">
@@ -449,13 +449,13 @@
         <v>-15.6631846713398</v>
       </c>
       <c r="E3">
-        <v>-10.59198051185036</v>
+        <v>-8.973168794432407</v>
       </c>
       <c r="F3">
-        <v>-2.855705647984495</v>
+        <v>-3.982053372919039</v>
       </c>
       <c r="G3">
-        <v>-6.73952297742646</v>
+        <v>-4.863353301951566</v>
       </c>
     </row>
     <row r="4" spans="1:7">
@@ -472,13 +472,13 @@
         <v>-15.25550151414335</v>
       </c>
       <c r="E4">
-        <v>-11.61010826604687</v>
+        <v>-7.514542788087778</v>
       </c>
       <c r="F4">
-        <v>-2.636997601195162</v>
+        <v>-3.785060977594094</v>
       </c>
       <c r="G4">
-        <v>-6.562884977216872</v>
+        <v>-4.54636761197985</v>
       </c>
     </row>
     <row r="5" spans="1:7">
@@ -495,13 +495,13 @@
         <v>-14.77908021507716</v>
       </c>
       <c r="E5">
-        <v>-12.22469464447186</v>
+        <v>-10.22616132456273</v>
       </c>
       <c r="F5">
-        <v>-2.945149446669175</v>
+        <v>-3.262727284819644</v>
       </c>
       <c r="G5">
-        <v>-5.998422994788717</v>
+        <v>-4.16534560205401</v>
       </c>
     </row>
     <row r="6" spans="1:7">
@@ -518,13 +518,13 @@
         <v>-14.23719441712038</v>
       </c>
       <c r="E6">
-        <v>-13.55180018021172</v>
+        <v>-9.951459562783443</v>
       </c>
       <c r="F6">
-        <v>-2.378982692775588</v>
+        <v>-2.877324380462757</v>
       </c>
       <c r="G6">
-        <v>-5.023119260902488</v>
+        <v>-3.929616082780383</v>
       </c>
     </row>
     <row r="7" spans="1:7">
@@ -541,13 +541,13 @@
         <v>-13.64698766884304</v>
       </c>
       <c r="E7">
-        <v>-13.85222820282859</v>
+        <v>-10.99881408822546</v>
       </c>
       <c r="F7">
-        <v>-2.583204250424764</v>
+        <v>-2.894710983880116</v>
       </c>
       <c r="G7">
-        <v>-5.164267568725122</v>
+        <v>-3.081771400370785</v>
       </c>
     </row>
     <row r="8" spans="1:7">
@@ -564,13 +564,13 @@
         <v>-13.01692050274674</v>
       </c>
       <c r="E8">
-        <v>-15.38933266372615</v>
+        <v>-10.40693800694893</v>
       </c>
       <c r="F8">
-        <v>-2.507169234889201</v>
+        <v>-2.754920671188088</v>
       </c>
       <c r="G8">
-        <v>-4.353746781554207</v>
+        <v>-2.241919773679994</v>
       </c>
     </row>
     <row r="9" spans="1:7">
@@ -587,13 +587,13 @@
         <v>-12.36247933234167</v>
       </c>
       <c r="E9">
-        <v>-15.09722344786137</v>
+        <v>-12.73042556470047</v>
       </c>
       <c r="F9">
-        <v>-2.634237481009034</v>
+        <v>-2.798296473500879</v>
       </c>
       <c r="G9">
-        <v>-4.264550054682262</v>
+        <v>-1.338297605981394</v>
       </c>
     </row>
     <row r="10" spans="1:7">
@@ -610,13 +610,13 @@
         <v>-11.69880328852548</v>
       </c>
       <c r="E10">
-        <v>-15.73610508933751</v>
+        <v>-13.13451035735291</v>
       </c>
       <c r="F10">
-        <v>-2.349415775067466</v>
+        <v>-2.161833633438323</v>
       </c>
       <c r="G10">
-        <v>-3.527489255784195</v>
+        <v>-2.042976029309301</v>
       </c>
     </row>
     <row r="11" spans="1:7">
@@ -633,13 +633,13 @@
         <v>-11.0345863649659</v>
       </c>
       <c r="E11">
-        <v>-16.69427131919846</v>
+        <v>-14.07239355213351</v>
       </c>
       <c r="F11">
-        <v>-2.061919270782258</v>
+        <v>-2.353451581053905</v>
       </c>
       <c r="G11">
-        <v>-3.221771280647612</v>
+        <v>-1.380592551882637</v>
       </c>
     </row>
     <row r="12" spans="1:7">
@@ -656,13 +656,13 @@
         <v>-10.3820248803036</v>
       </c>
       <c r="E12">
-        <v>-18.2581118906373</v>
+        <v>-14.78669239973339</v>
       </c>
       <c r="F12">
-        <v>-2.011490748402033</v>
+        <v>-2.288786736489167</v>
       </c>
       <c r="G12">
-        <v>-2.450513590657013</v>
+        <v>0.4766641625236179</v>
       </c>
     </row>
     <row r="13" spans="1:7">
@@ -679,13 +679,13 @@
         <v>-9.746830577828794</v>
       </c>
       <c r="E13">
-        <v>-17.99537435718628</v>
+        <v>-14.58395261840999</v>
       </c>
       <c r="F13">
-        <v>-2.063059932695913</v>
+        <v>-1.769541197392353</v>
       </c>
       <c r="G13">
-        <v>-1.551029043344874</v>
+        <v>0.1727049221428972</v>
       </c>
     </row>
     <row r="14" spans="1:7">
@@ -702,13 +702,13 @@
         <v>-9.152527241815486</v>
       </c>
       <c r="E14">
-        <v>-18.43866667779713</v>
+        <v>-16.4963362487972</v>
       </c>
       <c r="F14">
-        <v>-1.978987268250985</v>
+        <v>-2.256467153901542</v>
       </c>
       <c r="G14">
-        <v>-0.7279739898168801</v>
+        <v>0.6695278033446593</v>
       </c>
     </row>
     <row r="15" spans="1:7">
@@ -725,13 +725,13 @@
         <v>-8.604854793150903</v>
       </c>
       <c r="E15">
-        <v>-19.75592731104431</v>
+        <v>-17.24062265127587</v>
       </c>
       <c r="F15">
-        <v>-2.110714252644163</v>
+        <v>-2.387109805364454</v>
       </c>
       <c r="G15">
-        <v>-0.9484884847193622</v>
+        <v>1.68151559426548</v>
       </c>
     </row>
     <row r="16" spans="1:7">
@@ -748,13 +748,13 @@
         <v>-8.112855357644531</v>
       </c>
       <c r="E16">
-        <v>-20.6193623931388</v>
+        <v>-18.34721867368623</v>
       </c>
       <c r="F16">
-        <v>-1.748362328004978</v>
+        <v>-1.863599002510625</v>
       </c>
       <c r="G16">
-        <v>-0.6078025314237768</v>
+        <v>2.408457105874219</v>
       </c>
     </row>
     <row r="17" spans="1:7">
@@ -771,13 +771,13 @@
         <v>-7.676241077454224</v>
       </c>
       <c r="E17">
-        <v>-21.83904346846871</v>
+        <v>-19.38758123526041</v>
       </c>
       <c r="F17">
-        <v>-1.836719308657184</v>
+        <v>-1.721854571115394</v>
       </c>
       <c r="G17">
-        <v>0.06563538143665665</v>
+        <v>1.950218108989967</v>
       </c>
     </row>
     <row r="18" spans="1:7">
@@ -794,13 +794,13 @@
         <v>-7.300769685562674</v>
       </c>
       <c r="E18">
-        <v>-23.12674675186783</v>
+        <v>-19.66685222731343</v>
       </c>
       <c r="F18">
-        <v>-1.562455973631699</v>
+        <v>-1.984726197617581</v>
       </c>
       <c r="G18">
-        <v>0.3127704268509137</v>
+        <v>2.991690956843958</v>
       </c>
     </row>
     <row r="19" spans="1:7">
@@ -817,13 +817,13 @@
         <v>-6.984116884847909</v>
       </c>
       <c r="E19">
-        <v>-23.23720076138891</v>
+        <v>-21.0550649913128</v>
       </c>
       <c r="F19">
-        <v>-1.831376338909128</v>
+        <v>-1.158907681316489</v>
       </c>
       <c r="G19">
-        <v>0.9812241641625506</v>
+        <v>2.711294168481609</v>
       </c>
     </row>
     <row r="20" spans="1:7">
@@ -840,13 +840,13 @@
         <v>-6.718674830758482</v>
       </c>
       <c r="E20">
-        <v>-24.51046274117757</v>
+        <v>-22.24541966896903</v>
       </c>
       <c r="F20">
-        <v>-1.602901840440788</v>
+        <v>-1.139122125900623</v>
       </c>
       <c r="G20">
-        <v>1.303705900246337</v>
+        <v>3.937795100072687</v>
       </c>
     </row>
     <row r="21" spans="1:7">
@@ -863,13 +863,13 @@
         <v>-6.494009849162948</v>
       </c>
       <c r="E21">
-        <v>-23.98157320487374</v>
+        <v>-22.3846747731789</v>
       </c>
       <c r="F21">
-        <v>-1.154082441195182</v>
+        <v>-1.555464552752071</v>
       </c>
       <c r="G21">
-        <v>1.797546151050564</v>
+        <v>3.493045205019313</v>
       </c>
     </row>
     <row r="22" spans="1:7">
@@ -886,13 +886,13 @@
         <v>-6.298878440316868</v>
       </c>
       <c r="E22">
-        <v>-25.33922782626934</v>
+        <v>-22.47288944684832</v>
       </c>
       <c r="F22">
-        <v>-1.2860877570357</v>
+        <v>-1.971456580192135</v>
       </c>
       <c r="G22">
-        <v>1.489813505876482</v>
+        <v>4.246653204241659</v>
       </c>
     </row>
     <row r="23" spans="1:7">
@@ -909,13 +909,13 @@
         <v>-6.129303439019097</v>
       </c>
       <c r="E23">
-        <v>-25.17344492132253</v>
+        <v>-22.95704218843038</v>
       </c>
       <c r="F23">
-        <v>-1.068092106212774</v>
+        <v>-1.339449528389238</v>
       </c>
       <c r="G23">
-        <v>2.271633448066933</v>
+        <v>3.971942772841829</v>
       </c>
     </row>
     <row r="24" spans="1:7">
@@ -932,13 +932,13 @@
         <v>-5.975185647558346</v>
       </c>
       <c r="E24">
-        <v>-26.00484557828677</v>
+        <v>-24.96959113539325</v>
       </c>
       <c r="F24">
-        <v>-1.120616398122082</v>
+        <v>-1.110069624349638</v>
       </c>
       <c r="G24">
-        <v>2.001926879545256</v>
+        <v>4.579359226704675</v>
       </c>
     </row>
     <row r="25" spans="1:7">
@@ -955,13 +955,13 @@
         <v>-5.832856736899749</v>
       </c>
       <c r="E25">
-        <v>-26.71702510005106</v>
+        <v>-23.50377844079845</v>
       </c>
       <c r="F25">
-        <v>-0.8312138204430325</v>
+        <v>-1.036986910237652</v>
       </c>
       <c r="G25">
-        <v>1.825167474137969</v>
+        <v>3.454707412318761</v>
       </c>
     </row>
     <row r="26" spans="1:7">
@@ -978,13 +978,13 @@
         <v>-5.696814722161894</v>
       </c>
       <c r="E26">
-        <v>-26.36966850129271</v>
+        <v>-24.15585605553294</v>
       </c>
       <c r="F26">
-        <v>-1.059290702558029</v>
+        <v>-1.272792460220768</v>
       </c>
       <c r="G26">
-        <v>2.607578036209121</v>
+        <v>4.185645451786903</v>
       </c>
     </row>
     <row r="27" spans="1:7">
@@ -1001,13 +1001,13 @@
         <v>-5.571344184558825</v>
       </c>
       <c r="E27">
-        <v>-25.93642033603087</v>
+        <v>-23.89571333768831</v>
       </c>
       <c r="F27">
-        <v>-1.138137197058694</v>
+        <v>-1.001349716201815</v>
       </c>
       <c r="G27">
-        <v>2.935562380848096</v>
+        <v>5.040879445148371</v>
       </c>
     </row>
     <row r="28" spans="1:7">
@@ -1024,13 +1024,13 @@
         <v>-5.454223335438075</v>
       </c>
       <c r="E28">
-        <v>-25.52164381624632</v>
+        <v>-24.45608482529347</v>
       </c>
       <c r="F28">
-        <v>-0.8544652650722118</v>
+        <v>-0.833520823659829</v>
       </c>
       <c r="G28">
-        <v>2.527066702805026</v>
+        <v>4.629420824037123</v>
       </c>
     </row>
     <row r="29" spans="1:7">
@@ -1047,13 +1047,13 @@
         <v>-5.346533423155754</v>
       </c>
       <c r="E29">
-        <v>-26.46497023678413</v>
+        <v>-24.06028714007506</v>
       </c>
       <c r="F29">
-        <v>-1.123113097474119</v>
+        <v>-0.867169107561545</v>
       </c>
       <c r="G29">
-        <v>2.429164895135874</v>
+        <v>4.425430560908004</v>
       </c>
     </row>
     <row r="30" spans="1:7">
@@ -1070,13 +1070,13 @@
         <v>-5.247026102937944</v>
       </c>
       <c r="E30">
-        <v>-26.60826926828285</v>
+        <v>-24.63539881057519</v>
       </c>
       <c r="F30">
-        <v>-0.940501160261774</v>
+        <v>-0.8852432559232274</v>
       </c>
       <c r="G30">
-        <v>2.417880774192944</v>
+        <v>4.341680661824737</v>
       </c>
     </row>
     <row r="31" spans="1:7">
@@ -1093,13 +1093,13 @@
         <v>-5.156923195463903</v>
       </c>
       <c r="E31">
-        <v>-26.69049277084012</v>
+        <v>-22.28733069591002</v>
       </c>
       <c r="F31">
-        <v>-0.9418696232111988</v>
+        <v>-1.164791574978574</v>
       </c>
       <c r="G31">
-        <v>2.347856224892834</v>
+        <v>3.34166932959589</v>
       </c>
     </row>
     <row r="32" spans="1:7">
@@ -1116,13 +1116,13 @@
         <v>-5.077371673294109</v>
       </c>
       <c r="E32">
-        <v>-25.6793252811934</v>
+        <v>-22.6318071851995</v>
       </c>
       <c r="F32">
-        <v>-1.000158523876589</v>
+        <v>-0.9680029580347176</v>
       </c>
       <c r="G32">
-        <v>2.494789326324768</v>
+        <v>2.984554299952165</v>
       </c>
     </row>
     <row r="33" spans="1:7">
@@ -1139,13 +1139,13 @@
         <v>-5.007199037715295</v>
       </c>
       <c r="E33">
-        <v>-26.43409510099983</v>
+        <v>-22.89599835880698</v>
       </c>
       <c r="F33">
-        <v>-1.072543752635418</v>
+        <v>-0.8667284161032557</v>
       </c>
       <c r="G33">
-        <v>1.5951210306053</v>
+        <v>3.559119163561851</v>
       </c>
     </row>
     <row r="34" spans="1:7">
@@ -1162,13 +1162,13 @@
         <v>-4.94738233998147</v>
       </c>
       <c r="E34">
-        <v>-24.33000305197191</v>
+        <v>-22.76604926868287</v>
       </c>
       <c r="F34">
-        <v>-0.9830543937435846</v>
+        <v>-1.264362165162477</v>
       </c>
       <c r="G34">
-        <v>1.423710016339908</v>
+        <v>3.803327359345083</v>
       </c>
     </row>
     <row r="35" spans="1:7">
@@ -1185,13 +1185,13 @@
         <v>-4.895644660616465</v>
       </c>
       <c r="E35">
-        <v>-23.91176224957149</v>
+        <v>-22.71815612757775</v>
       </c>
       <c r="F35">
-        <v>-0.8427778293861136</v>
+        <v>-1.399956796959325</v>
       </c>
       <c r="G35">
-        <v>1.851942242063038</v>
+        <v>2.730417127730053</v>
       </c>
     </row>
     <row r="36" spans="1:7">
@@ -1208,13 +1208,13 @@
         <v>-4.855463631917591</v>
       </c>
       <c r="E36">
-        <v>-23.59510417611113</v>
+        <v>-21.01280074339921</v>
       </c>
       <c r="F36">
-        <v>-1.28442191018867</v>
+        <v>-0.877539439077192</v>
       </c>
       <c r="G36">
-        <v>1.186631915005349</v>
+        <v>1.491309742907588</v>
       </c>
     </row>
     <row r="37" spans="1:7">
@@ -1231,13 +1231,13 @@
         <v>-4.822797369429069</v>
       </c>
       <c r="E37">
-        <v>-22.54142790095441</v>
+        <v>-19.28099454254187</v>
       </c>
       <c r="F37">
-        <v>-0.9740425847685288</v>
+        <v>-0.9340398945199379</v>
       </c>
       <c r="G37">
-        <v>0.7876025611612775</v>
+        <v>1.498974676470451</v>
       </c>
     </row>
     <row r="38" spans="1:7">
@@ -1254,13 +1254,13 @@
         <v>-4.799129324475162</v>
       </c>
       <c r="E38">
-        <v>-22.48512991209105</v>
+        <v>-18.52179587515593</v>
       </c>
       <c r="F38">
-        <v>-0.9678107767972681</v>
+        <v>-0.2530763292115903</v>
       </c>
       <c r="G38">
-        <v>0.4488229975917294</v>
+        <v>1.955582906239659</v>
       </c>
     </row>
     <row r="39" spans="1:7">
@@ -1277,13 +1277,13 @@
         <v>-4.783360261307601</v>
       </c>
       <c r="E39">
-        <v>-21.02539442961454</v>
+        <v>-18.3744166885763</v>
       </c>
       <c r="F39">
-        <v>-0.703019823022795</v>
+        <v>-0.7553950087995993</v>
       </c>
       <c r="G39">
-        <v>0.4622891308716905</v>
+        <v>1.828317446835036</v>
       </c>
     </row>
     <row r="40" spans="1:7">
@@ -1300,13 +1300,13 @@
         <v>-4.780010130832729</v>
       </c>
       <c r="E40">
-        <v>-20.65380596644114</v>
+        <v>-19.06010916586973</v>
       </c>
       <c r="F40">
-        <v>-0.6791818942724336</v>
+        <v>-0.7450602970822727</v>
       </c>
       <c r="G40">
-        <v>-0.08983873971451233</v>
+        <v>1.114956911260839</v>
       </c>
     </row>
     <row r="41" spans="1:7">
@@ -1323,13 +1323,13 @@
         <v>-4.790914885862025</v>
       </c>
       <c r="E41">
-        <v>-20.92359433392211</v>
+        <v>-17.66491802342455</v>
       </c>
       <c r="F41">
-        <v>-0.7304984265084602</v>
+        <v>-0.5414169398802506</v>
       </c>
       <c r="G41">
-        <v>-0.2744730768644665</v>
+        <v>0.6503621882159427</v>
       </c>
     </row>
     <row r="42" spans="1:7">
@@ -1346,13 +1346,13 @@
         <v>-4.820764507134743</v>
       </c>
       <c r="E42">
-        <v>-19.58296677479535</v>
+        <v>-16.21018197625251</v>
       </c>
       <c r="F42">
-        <v>-0.8250110053308698</v>
+        <v>-0.3726461936012821</v>
       </c>
       <c r="G42">
-        <v>-0.7325677000001026</v>
+        <v>1.496635165498567</v>
       </c>
     </row>
     <row r="43" spans="1:7">
@@ -1369,13 +1369,13 @@
         <v>-4.875691497076041</v>
       </c>
       <c r="E43">
-        <v>-18.47170642415709</v>
+        <v>-15.67147470830004</v>
       </c>
       <c r="F43">
-        <v>-0.2813468519343318</v>
+        <v>-1.246984673786549</v>
       </c>
       <c r="G43">
-        <v>0.04448134604291656</v>
+        <v>1.527924894289432</v>
       </c>
     </row>
     <row r="44" spans="1:7">
@@ -1392,13 +1392,13 @@
         <v>-4.961331784866748</v>
       </c>
       <c r="E44">
-        <v>-17.97415392798633</v>
+        <v>-15.02260778163699</v>
       </c>
       <c r="F44">
-        <v>-0.3930795323261376</v>
+        <v>-0.5080420172214586</v>
       </c>
       <c r="G44">
-        <v>-1.255847070635668</v>
+        <v>0.3944662812379683</v>
       </c>
     </row>
     <row r="45" spans="1:7">
@@ -1415,13 +1415,13 @@
         <v>-5.083399371784383</v>
       </c>
       <c r="E45">
-        <v>-17.41487833109103</v>
+        <v>-11.76915733014427</v>
       </c>
       <c r="F45">
-        <v>-0.1272415221545258</v>
+        <v>0.1517940374784877</v>
       </c>
       <c r="G45">
-        <v>-1.478829044150852</v>
+        <v>0.04406134968330764</v>
       </c>
     </row>
     <row r="46" spans="1:7">
@@ -1438,13 +1438,13 @@
         <v>-5.240882365292251</v>
       </c>
       <c r="E46">
-        <v>-16.03164236002609</v>
+        <v>-13.62321874378669</v>
       </c>
       <c r="F46">
-        <v>0.007497406115230573</v>
+        <v>-0.3011174967369477</v>
       </c>
       <c r="G46">
-        <v>-0.4659093863071495</v>
+        <v>-0.2007046537650304</v>
       </c>
     </row>
     <row r="47" spans="1:7">
@@ -1461,13 +1461,13 @@
         <v>-5.437056890404767</v>
       </c>
       <c r="E47">
-        <v>-16.21845549826452</v>
+        <v>-11.85103214020295</v>
       </c>
       <c r="F47">
-        <v>-0.3262493353704818</v>
+        <v>-0.321563260972845</v>
       </c>
       <c r="G47">
-        <v>-1.01155028187033</v>
+        <v>-0.1245114079331646</v>
       </c>
     </row>
     <row r="48" spans="1:7">
@@ -1484,13 +1484,13 @@
         <v>-5.66933157128143</v>
       </c>
       <c r="E48">
-        <v>-14.78990761627884</v>
+        <v>-11.62538280887474</v>
       </c>
       <c r="F48">
-        <v>0.02508944464848368</v>
+        <v>-0.3197681888109785</v>
       </c>
       <c r="G48">
-        <v>-1.765643901883474</v>
+        <v>-0.1926000365132019</v>
       </c>
     </row>
     <row r="49" spans="1:7">
@@ -1507,13 +1507,13 @@
         <v>-5.937810714696197</v>
       </c>
       <c r="E49">
-        <v>-14.62560099385853</v>
+        <v>-10.8717269936742</v>
       </c>
       <c r="F49">
-        <v>-0.06051818459383124</v>
+        <v>-0.3574497935969252</v>
       </c>
       <c r="G49">
-        <v>-1.935643990878305</v>
+        <v>-1.351153432051299</v>
       </c>
     </row>
     <row r="50" spans="1:7">
@@ -1530,13 +1530,13 @@
         <v>-6.231790846073372</v>
       </c>
       <c r="E50">
-        <v>-12.88841496588008</v>
+        <v>-10.15889990012681</v>
       </c>
       <c r="F50">
-        <v>0.2596905484279289</v>
+        <v>-0.005037449423931546</v>
       </c>
       <c r="G50">
-        <v>-2.324170154510594</v>
+        <v>-0.5481466422515124</v>
       </c>
     </row>
     <row r="51" spans="1:7">
@@ -1553,13 +1553,13 @@
         <v>-6.547151406315789</v>
       </c>
       <c r="E51">
-        <v>-13.23103930930042</v>
+        <v>-9.555127517632133</v>
       </c>
       <c r="F51">
-        <v>0.2608436358526258</v>
+        <v>-0.08246495056360134</v>
       </c>
       <c r="G51">
-        <v>-2.393079088480493</v>
+        <v>-1.57031606367129</v>
       </c>
     </row>
     <row r="52" spans="1:7">
@@ -1576,13 +1576,13 @@
         <v>-6.876029196245998</v>
       </c>
       <c r="E52">
-        <v>-12.44902618986384</v>
+        <v>-8.096229802847043</v>
       </c>
       <c r="F52">
-        <v>0.05438631458329379</v>
+        <v>-0.1101986912093288</v>
       </c>
       <c r="G52">
-        <v>-2.789722994250848</v>
+        <v>-1.401451277336027</v>
       </c>
     </row>
     <row r="53" spans="1:7">
@@ -1599,13 +1599,13 @@
         <v>-7.211749120810845</v>
       </c>
       <c r="E53">
-        <v>-12.22300099519299</v>
+        <v>-8.412312760108426</v>
       </c>
       <c r="F53">
-        <v>0.3318670286012526</v>
+        <v>-0.3035181054702606</v>
       </c>
       <c r="G53">
-        <v>-2.970193461241867</v>
+        <v>-1.301137771820683</v>
       </c>
     </row>
     <row r="54" spans="1:7">
@@ -1622,13 +1622,13 @@
         <v>-7.54464103842581</v>
       </c>
       <c r="E54">
-        <v>-11.4639427105013</v>
+        <v>-7.871735232390793</v>
       </c>
       <c r="F54">
-        <v>0.3323035782225279</v>
+        <v>0.2409073175694501</v>
       </c>
       <c r="G54">
-        <v>-4.02092919755817</v>
+        <v>-1.949192154697252</v>
       </c>
     </row>
     <row r="55" spans="1:7">
@@ -1645,13 +1645,13 @@
         <v>-7.86514423752242</v>
       </c>
       <c r="E55">
-        <v>-10.12035352937352</v>
+        <v>-7.286905456670204</v>
       </c>
       <c r="F55">
-        <v>0.2878252188966113</v>
+        <v>-0.2773077324782814</v>
       </c>
       <c r="G55">
-        <v>-4.153923669805583</v>
+        <v>-2.385076189097007</v>
       </c>
     </row>
     <row r="56" spans="1:7">
@@ -1668,13 +1668,13 @@
         <v>-8.169192014335495</v>
       </c>
       <c r="E56">
-        <v>-10.15286797274859</v>
+        <v>-6.948143901578407</v>
       </c>
       <c r="F56">
-        <v>0.3213740987099912</v>
+        <v>-0.02895655817976727</v>
       </c>
       <c r="G56">
-        <v>-4.016010646440562</v>
+        <v>-3.744847215546492</v>
       </c>
     </row>
     <row r="57" spans="1:7">
@@ -1691,13 +1691,13 @@
         <v>-8.450672701529493</v>
       </c>
       <c r="E57">
-        <v>-8.966629677965331</v>
+        <v>-5.234252343895408</v>
       </c>
       <c r="F57">
-        <v>0.3112017470036133</v>
+        <v>-0.07291718787893424</v>
       </c>
       <c r="G57">
-        <v>-4.276329640080668</v>
+        <v>-3.55600635235733</v>
       </c>
     </row>
     <row r="58" spans="1:7">
@@ -1714,13 +1714,13 @@
         <v>-8.708655040812262</v>
       </c>
       <c r="E58">
-        <v>-9.364510461227265</v>
+        <v>-3.18999955040484</v>
       </c>
       <c r="F58">
-        <v>0.3502625835152212</v>
+        <v>-0.1863190285873809</v>
       </c>
       <c r="G58">
-        <v>-5.169681584298206</v>
+        <v>-2.803605842668859</v>
       </c>
     </row>
     <row r="59" spans="1:7">
@@ -1737,13 +1737,13 @@
         <v>-8.934367540275202</v>
       </c>
       <c r="E59">
-        <v>-9.355802205710514</v>
+        <v>-4.900218515667619</v>
       </c>
       <c r="F59">
-        <v>0.4453409372737429</v>
+        <v>-0.2540206680507818</v>
       </c>
       <c r="G59">
-        <v>-5.05590522672446</v>
+        <v>-5.043512052894437</v>
       </c>
     </row>
     <row r="60" spans="1:7">
@@ -1760,13 +1760,13 @@
         <v>-9.129408596580909</v>
       </c>
       <c r="E60">
-        <v>-8.950376984751802</v>
+        <v>-3.932537961916556</v>
       </c>
       <c r="F60">
-        <v>0.4899021333399395</v>
+        <v>0.3129214377318251</v>
       </c>
       <c r="G60">
-        <v>-5.122412306512845</v>
+        <v>-3.790111666959032</v>
       </c>
     </row>
     <row r="61" spans="1:7">
@@ -1783,13 +1783,13 @@
         <v>-9.29095087466604</v>
       </c>
       <c r="E61">
-        <v>-7.856822967483534</v>
+        <v>-2.324703265493195</v>
       </c>
       <c r="F61">
-        <v>0.4445299655864021</v>
+        <v>0.05579371080065015</v>
       </c>
       <c r="G61">
-        <v>-5.820803909332856</v>
+        <v>-4.407768813308905</v>
       </c>
     </row>
     <row r="62" spans="1:7">
@@ -1806,13 +1806,13 @@
         <v>-9.4219196474365</v>
       </c>
       <c r="E62">
-        <v>-7.659734721721705</v>
+        <v>-3.621730676874108</v>
       </c>
       <c r="F62">
-        <v>0.3903837303024125</v>
+        <v>-0.2683779318761028</v>
       </c>
       <c r="G62">
-        <v>-5.527000049678616</v>
+        <v>-3.669277401810921</v>
       </c>
     </row>
     <row r="63" spans="1:7">
@@ -1829,13 +1829,13 @@
         <v>-9.519475518632245</v>
       </c>
       <c r="E63">
-        <v>-7.637087823209345</v>
+        <v>-3.771301644873453</v>
       </c>
       <c r="F63">
-        <v>0.2335356760519373</v>
+        <v>-0.4320500767908403</v>
       </c>
       <c r="G63">
-        <v>-5.555257929748554</v>
+        <v>-4.540920784191171</v>
       </c>
     </row>
     <row r="64" spans="1:7">
@@ -1852,13 +1852,13 @@
         <v>-9.585298642066837</v>
       </c>
       <c r="E64">
-        <v>-7.34108864817198</v>
+        <v>-3.543274864691219</v>
       </c>
       <c r="F64">
-        <v>0.2061763574722752</v>
+        <v>-0.8300068891371536</v>
       </c>
       <c r="G64">
-        <v>-6.537156918969266</v>
+        <v>-4.889048547983577</v>
       </c>
     </row>
     <row r="65" spans="1:7">
@@ -1875,13 +1875,13 @@
         <v>-9.621195160167808</v>
       </c>
       <c r="E65">
-        <v>-7.271490531148094</v>
+        <v>-4.007805728398044</v>
       </c>
       <c r="F65">
-        <v>0.4084537368270809</v>
+        <v>-0.8228920415145087</v>
       </c>
       <c r="G65">
-        <v>-5.795361317360921</v>
+        <v>-2.813462632233431</v>
       </c>
     </row>
     <row r="66" spans="1:7">
@@ -1898,13 +1898,13 @@
         <v>-9.629273241417945</v>
       </c>
       <c r="E66">
-        <v>-7.404894846940056</v>
+        <v>-4.288457905023416</v>
       </c>
       <c r="F66">
-        <v>0.1952402510205161</v>
+        <v>-0.1649189851034585</v>
       </c>
       <c r="G66">
-        <v>-5.745444093777089</v>
+        <v>-5.38982530116447</v>
       </c>
     </row>
     <row r="67" spans="1:7">
@@ -1921,13 +1921,13 @@
         <v>-9.613393593394258</v>
       </c>
       <c r="E67">
-        <v>-6.676231679787842</v>
+        <v>-2.85952510274708</v>
       </c>
       <c r="F67">
-        <v>0.2613414846617083</v>
+        <v>-0.3284544493967341</v>
       </c>
       <c r="G67">
-        <v>-6.091051879411841</v>
+        <v>-4.959981995655653</v>
       </c>
     </row>
     <row r="68" spans="1:7">
@@ -1944,13 +1944,13 @@
         <v>-9.571626069077166</v>
       </c>
       <c r="E68">
-        <v>-7.2814124176989</v>
+        <v>-2.967379768187765</v>
       </c>
       <c r="F68">
-        <v>0.09581462513210266</v>
+        <v>-0.5679561747311412</v>
       </c>
       <c r="G68">
-        <v>-5.737647911351848</v>
+        <v>-3.721192889324455</v>
       </c>
     </row>
     <row r="69" spans="1:7">
@@ -1967,13 +1967,13 @@
         <v>-9.507689111823568</v>
       </c>
       <c r="E69">
-        <v>-7.15333358733996</v>
+        <v>-2.75718159017373</v>
       </c>
       <c r="F69">
-        <v>-0.008384882098644348</v>
+        <v>-0.4659833190791192</v>
       </c>
       <c r="G69">
-        <v>-5.928224540745957</v>
+        <v>-4.849007801293673</v>
       </c>
     </row>
     <row r="70" spans="1:7">
@@ -1990,13 +1990,13 @@
         <v>-9.41939525346011</v>
       </c>
       <c r="E70">
-        <v>-6.948152958526423</v>
+        <v>-2.282122024399071</v>
       </c>
       <c r="F70">
-        <v>-0.04162726597298851</v>
+        <v>-0.2941616956556402</v>
       </c>
       <c r="G70">
-        <v>-6.144936099861042</v>
+        <v>-2.753399871587795</v>
       </c>
     </row>
     <row r="71" spans="1:7">
@@ -2013,13 +2013,13 @@
         <v>-9.313966866841767</v>
       </c>
       <c r="E71">
-        <v>-7.667913145779558</v>
+        <v>-2.484241404783422</v>
       </c>
       <c r="F71">
-        <v>-0.3094210515826099</v>
+        <v>-0.7123671207959846</v>
       </c>
       <c r="G71">
-        <v>-5.765370952307596</v>
+        <v>-4.483807841727477</v>
       </c>
     </row>
     <row r="72" spans="1:7">
@@ -2036,13 +2036,13 @@
         <v>-9.187920604588198</v>
       </c>
       <c r="E72">
-        <v>-7.199682518808466</v>
+        <v>-3.278096483750059</v>
       </c>
       <c r="F72">
-        <v>0.0243836756212985</v>
+        <v>-0.1108721539078048</v>
       </c>
       <c r="G72">
-        <v>-5.726691912564863</v>
+        <v>-4.044813209289368</v>
       </c>
     </row>
     <row r="73" spans="1:7">
@@ -2059,13 +2059,13 @@
         <v>-9.045339489058017</v>
       </c>
       <c r="E73">
-        <v>-7.578140677051501</v>
+        <v>-2.988699823815877</v>
       </c>
       <c r="F73">
-        <v>0.03312129498602768</v>
+        <v>-0.8168963182530458</v>
       </c>
       <c r="G73">
-        <v>-5.805050764625961</v>
+        <v>-2.062532109803592</v>
       </c>
     </row>
     <row r="74" spans="1:7">
@@ -2082,13 +2082,13 @@
         <v>-8.885922051188986</v>
       </c>
       <c r="E74">
-        <v>-7.275452945904806</v>
+        <v>-4.609431614213082</v>
       </c>
       <c r="F74">
-        <v>-0.1744626059511116</v>
+        <v>-0.4222844534792369</v>
       </c>
       <c r="G74">
-        <v>-5.750444675433682</v>
+        <v>-3.220770508071982</v>
       </c>
     </row>
     <row r="75" spans="1:7">
@@ -2105,13 +2105,13 @@
         <v>-8.714664883379246</v>
       </c>
       <c r="E75">
-        <v>-8.887127788286671</v>
+        <v>-5.5897783097636</v>
       </c>
       <c r="F75">
-        <v>-0.5312114534777607</v>
+        <v>-0.3001690160607422</v>
       </c>
       <c r="G75">
-        <v>-5.064032812527205</v>
+        <v>-2.118457250062767</v>
       </c>
     </row>
     <row r="76" spans="1:7">
@@ -2128,13 +2128,13 @@
         <v>-8.534201098653437</v>
       </c>
       <c r="E76">
-        <v>-8.704729912205725</v>
+        <v>-4.365201954031405</v>
       </c>
       <c r="F76">
-        <v>-0.1833451896113307</v>
+        <v>0.07761125145558352</v>
       </c>
       <c r="G76">
-        <v>-4.500250042961854</v>
+        <v>-2.28513674283944</v>
       </c>
     </row>
     <row r="77" spans="1:7">
@@ -2151,13 +2151,13 @@
         <v>-8.345108969451758</v>
       </c>
       <c r="E77">
-        <v>-9.185382143379856</v>
+        <v>-4.892352556316296</v>
       </c>
       <c r="F77">
-        <v>-0.09403558644590483</v>
+        <v>-0.7153475867112572</v>
       </c>
       <c r="G77">
-        <v>-4.282570523486732</v>
+        <v>-2.462581923552651</v>
       </c>
     </row>
     <row r="78" spans="1:7">
@@ -2174,13 +2174,13 @@
         <v>-8.1495200363143</v>
       </c>
       <c r="E78">
-        <v>-9.571434552533754</v>
+        <v>-6.144833368883756</v>
       </c>
       <c r="F78">
-        <v>-0.3243540307528766</v>
+        <v>-0.5579677205881848</v>
       </c>
       <c r="G78">
-        <v>-4.58111246707281</v>
+        <v>-1.797209253285332</v>
       </c>
     </row>
     <row r="79" spans="1:7">
@@ -2197,13 +2197,13 @@
         <v>-7.946871029976188</v>
       </c>
       <c r="E79">
-        <v>-10.90173719092303</v>
+        <v>-6.673700262817554</v>
       </c>
       <c r="F79">
-        <v>-0.1393820748099554</v>
+        <v>-0.344068346572102</v>
       </c>
       <c r="G79">
-        <v>-3.564704870711418</v>
+        <v>-1.037957552980741</v>
       </c>
     </row>
     <row r="80" spans="1:7">
@@ -2220,13 +2220,13 @@
         <v>-7.743977668500751</v>
       </c>
       <c r="E80">
-        <v>-11.19824808352326</v>
+        <v>-6.648150612466277</v>
       </c>
       <c r="F80">
-        <v>-0.3302056180862523</v>
+        <v>-0.006531824218581854</v>
       </c>
       <c r="G80">
-        <v>-3.623645453583723</v>
+        <v>-1.268089308273956</v>
       </c>
     </row>
     <row r="81" spans="1:7">
@@ -2243,13 +2243,13 @@
         <v>-7.538451913343451</v>
       </c>
       <c r="E81">
-        <v>-12.60199351336893</v>
+        <v>-7.192500359032301</v>
       </c>
       <c r="F81">
-        <v>-0.3368159899605923</v>
+        <v>-0.4443877808881361</v>
       </c>
       <c r="G81">
-        <v>-3.266746984562921</v>
+        <v>-0.1858669698732214</v>
       </c>
     </row>
     <row r="82" spans="1:7">
@@ -2266,13 +2266,13 @@
         <v>-7.33339032337222</v>
       </c>
       <c r="E82">
-        <v>-12.89549297075406</v>
+        <v>-8.996119100703281</v>
       </c>
       <c r="F82">
-        <v>-0.2735303771215157</v>
+        <v>-0.1041110191661552</v>
       </c>
       <c r="G82">
-        <v>-2.419210736979911</v>
+        <v>-0.5587613939963161</v>
       </c>
     </row>
     <row r="83" spans="1:7">
@@ -2289,13 +2289,13 @@
         <v>-7.127244774280293</v>
       </c>
       <c r="E83">
-        <v>-13.78917373074579</v>
+        <v>-9.350236711155087</v>
       </c>
       <c r="F83">
-        <v>-0.4270956113546965</v>
+        <v>-0.4753248182804893</v>
       </c>
       <c r="G83">
-        <v>-2.255904339966347</v>
+        <v>0.3286318518692695</v>
       </c>
     </row>
     <row r="84" spans="1:7">
@@ -2312,13 +2312,13 @@
         <v>-6.926445334195074</v>
       </c>
       <c r="E84">
-        <v>-14.58505756606786</v>
+        <v>-13.10705421944441</v>
       </c>
       <c r="F84">
-        <v>-0.4579539538437836</v>
+        <v>-0.2845476635787491</v>
       </c>
       <c r="G84">
-        <v>-1.883708816035414</v>
+        <v>1.96497048112123</v>
       </c>
     </row>
     <row r="85" spans="1:7">
@@ -2335,13 +2335,13 @@
         <v>-6.730991122472004</v>
       </c>
       <c r="E85">
-        <v>-15.93967358140432</v>
+        <v>-13.94882961036021</v>
       </c>
       <c r="F85">
-        <v>-0.2360740882691305</v>
+        <v>-0.5145720374577271</v>
       </c>
       <c r="G85">
-        <v>-0.9215627806025589</v>
+        <v>1.327123978516094</v>
       </c>
     </row>
     <row r="86" spans="1:7">
@@ -2358,13 +2358,13 @@
         <v>-6.543224960790756</v>
       </c>
       <c r="E86">
-        <v>-17.30084229862987</v>
+        <v>-14.80400928433872</v>
       </c>
       <c r="F86">
-        <v>-0.1585480114085275</v>
+        <v>0.1919259530419153</v>
       </c>
       <c r="G86">
-        <v>-1.339797124234061</v>
+        <v>2.121025378488421</v>
       </c>
     </row>
     <row r="87" spans="1:7">
@@ -2381,13 +2381,13 @@
         <v>-6.364980115206935</v>
       </c>
       <c r="E87">
-        <v>-17.83341348430195</v>
+        <v>-14.77139521453548</v>
       </c>
       <c r="F87">
-        <v>-0.1378230873578867</v>
+        <v>-0.9761946832810019</v>
       </c>
       <c r="G87">
-        <v>-1.189481083374339</v>
+        <v>2.421693553645019</v>
       </c>
     </row>
     <row r="88" spans="1:7">
@@ -2404,13 +2404,13 @@
         <v>-6.200425830110495</v>
       </c>
       <c r="E88">
-        <v>-20.60893784597314</v>
+        <v>-18.11059684983744</v>
       </c>
       <c r="F88">
-        <v>-0.4666211619792749</v>
+        <v>-0.5708422067624946</v>
       </c>
       <c r="G88">
-        <v>-0.4912699477400977</v>
+        <v>2.614035480238108</v>
       </c>
     </row>
     <row r="89" spans="1:7">
@@ -2427,13 +2427,13 @@
         <v>-6.055616134555864</v>
       </c>
       <c r="E89">
-        <v>-21.11823267524579</v>
+        <v>-18.7133005124663</v>
       </c>
       <c r="F89">
-        <v>-0.1505857439328187</v>
+        <v>-0.1974879062793267</v>
       </c>
       <c r="G89">
-        <v>-0.2490501722218888</v>
+        <v>1.982334705613812</v>
       </c>
     </row>
     <row r="90" spans="1:7">
@@ -2450,13 +2450,13 @@
         <v>-5.93175288580499</v>
       </c>
       <c r="E90">
-        <v>-22.76701383364651</v>
+        <v>-20.00977997849229</v>
       </c>
       <c r="F90">
-        <v>-0.09137818381772402</v>
+        <v>-0.3088511348094838</v>
       </c>
       <c r="G90">
-        <v>0.8555993155376503</v>
+        <v>3.167137873627466</v>
       </c>
     </row>
     <row r="91" spans="1:7">
@@ -2473,13 +2473,13 @@
         <v>-5.833671807367653</v>
       </c>
       <c r="E91">
-        <v>-24.79833330537117</v>
+        <v>-22.71377709321234</v>
       </c>
       <c r="F91">
-        <v>-0.3079018257658756</v>
+        <v>-0.2420515874477317</v>
       </c>
       <c r="G91">
-        <v>0.3412350238790967</v>
+        <v>2.86398253252881</v>
       </c>
     </row>
     <row r="92" spans="1:7">
@@ -2496,13 +2496,13 @@
         <v>-5.761352174421715</v>
       </c>
       <c r="E92">
-        <v>-26.17528828298746</v>
+        <v>-25.58601154579134</v>
       </c>
       <c r="F92">
-        <v>-0.7895452833474117</v>
+        <v>-0.6804169900700077</v>
       </c>
       <c r="G92">
-        <v>-0.1959271951744789</v>
+        <v>2.83685667389688</v>
       </c>
     </row>
     <row r="93" spans="1:7">
@@ -2519,13 +2519,13 @@
         <v>-5.721848210862028</v>
       </c>
       <c r="E93">
-        <v>-28.84773551929607</v>
+        <v>-26.78336271578943</v>
       </c>
       <c r="F93">
-        <v>-0.8438058333329878</v>
+        <v>-0.8306629561201708</v>
       </c>
       <c r="G93">
-        <v>0.619663079305778</v>
+        <v>3.113529275789259</v>
       </c>
     </row>
     <row r="94" spans="1:7">
@@ -2542,13 +2542,13 @@
         <v>-5.710947598910815</v>
       </c>
       <c r="E94">
-        <v>-30.67927230322434</v>
+        <v>-27.6334433280353</v>
       </c>
       <c r="F94">
-        <v>-0.6009351377713951</v>
+        <v>-0.6998687134225456</v>
       </c>
       <c r="G94">
-        <v>0.04385463272506262</v>
+        <v>1.698243261775529</v>
       </c>
     </row>
     <row r="95" spans="1:7">
@@ -2565,13 +2565,13 @@
         <v>-5.729128962362252</v>
       </c>
       <c r="E95">
-        <v>-32.63220615411323</v>
+        <v>-30.30894728429908</v>
       </c>
       <c r="F95">
-        <v>-0.8203771180796093</v>
+        <v>-1.269618984700643</v>
       </c>
       <c r="G95">
-        <v>0.6630408283216371</v>
+        <v>3.477945023402748</v>
       </c>
     </row>
     <row r="96" spans="1:7">
@@ -2588,13 +2588,13 @@
         <v>-5.773477281239893</v>
       </c>
       <c r="E96">
-        <v>-35.89432636909363</v>
+        <v>-31.36606972817564</v>
       </c>
       <c r="F96">
-        <v>-1.02894677622608</v>
+        <v>-1.330668833919564</v>
       </c>
       <c r="G96">
-        <v>0.7743693946120369</v>
+        <v>2.278651980982586</v>
       </c>
     </row>
     <row r="97" spans="1:7">
@@ -2611,13 +2611,13 @@
         <v>-5.840542576806985</v>
       </c>
       <c r="E97">
-        <v>-36.79127442308189</v>
+        <v>-34.54162136978841</v>
       </c>
       <c r="F97">
-        <v>-1.247299453399613</v>
+        <v>-1.713066421339094</v>
       </c>
       <c r="G97">
-        <v>0.565536048461178</v>
+        <v>2.526666393774774</v>
       </c>
     </row>
     <row r="98" spans="1:7">
@@ -2634,13 +2634,13 @@
         <v>-5.929333243860375</v>
       </c>
       <c r="E98">
-        <v>-39.57656217471362</v>
+        <v>-36.34072069439974</v>
       </c>
       <c r="F98">
-        <v>-1.470306727009476</v>
+        <v>-1.26762096252509</v>
       </c>
       <c r="G98">
-        <v>-0.1303880757461301</v>
+        <v>1.161153229596261</v>
       </c>
     </row>
     <row r="99" spans="1:7">
@@ -2657,13 +2657,13 @@
         <v>-6.028446709312203</v>
       </c>
       <c r="E99">
-        <v>-40.99156312670537</v>
+        <v>-39.87198396931501</v>
       </c>
       <c r="F99">
-        <v>-1.723392849382392</v>
+        <v>-1.938635835325816</v>
       </c>
       <c r="G99">
-        <v>-0.1404220512749121</v>
+        <v>1.944039568793533</v>
       </c>
     </row>
     <row r="100" spans="1:7">
@@ -2680,13 +2680,13 @@
         <v>-6.144268471236493</v>
       </c>
       <c r="E100">
-        <v>-44.2982774894763</v>
+        <v>-42.61444820649321</v>
       </c>
       <c r="F100">
-        <v>-1.741534095503702</v>
+        <v>-2.164278974011387</v>
       </c>
       <c r="G100">
-        <v>-0.3440415363678133</v>
+        <v>0.01108835423244769</v>
       </c>
     </row>
     <row r="101" spans="1:7">
@@ -2703,13 +2703,13 @@
         <v>-6.257508728514062</v>
       </c>
       <c r="E101">
-        <v>-45.7648622888894</v>
+        <v>-43.45948636293155</v>
       </c>
       <c r="F101">
-        <v>-2.259331648380422</v>
+        <v>-2.662740774971962</v>
       </c>
       <c r="G101">
-        <v>-0.2885856107916382</v>
+        <v>0.3809476484130561</v>
       </c>
     </row>
     <row r="102" spans="1:7">
@@ -2726,13 +2726,13 @@
         <v>-6.394944266705613</v>
       </c>
       <c r="E102">
-        <v>-47.86596328083527</v>
+        <v>-46.24354010539619</v>
       </c>
       <c r="F102">
-        <v>-2.49259908064136</v>
+        <v>-3.212115693243399</v>
       </c>
       <c r="G102">
-        <v>-1.011996528002415</v>
+        <v>1.04906341990407</v>
       </c>
     </row>
   </sheetData>
